--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.18576807741557</v>
+        <v>7.18018731258003</v>
       </c>
       <c r="D2" t="n">
-        <v>42.92114921781236</v>
+        <v>6.974686747894508</v>
       </c>
       <c r="E2" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F2" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.85565258888867</v>
+        <v>9.72654354569441</v>
       </c>
       <c r="D3" t="n">
-        <v>40.50407214040435</v>
+        <v>6.581911722815707</v>
       </c>
       <c r="E3" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F3" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.58108265011178</v>
+        <v>5.781925930643165</v>
       </c>
       <c r="D4" t="n">
-        <v>24.22065234464175</v>
+        <v>3.935856006004285</v>
       </c>
       <c r="E4" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F4" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.72762808534774</v>
+        <v>3.530739563869008</v>
       </c>
       <c r="D5" t="n">
-        <v>7.865065362896086</v>
+        <v>1.278073121470614</v>
       </c>
       <c r="E5" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F5" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.2198213273992</v>
+        <v>5.23572096570237</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63724086552148</v>
+        <v>5.141051640647241</v>
       </c>
       <c r="E6" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F6" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.66497924655204</v>
+        <v>4.170559127564706</v>
       </c>
       <c r="D7" t="n">
-        <v>31.86043878363366</v>
+        <v>5.177321302340471</v>
       </c>
       <c r="E7" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F7" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.7164132397937</v>
+        <v>3.853917151466477</v>
       </c>
       <c r="D8" t="n">
-        <v>19.19880128454427</v>
+        <v>3.119805208738444</v>
       </c>
       <c r="E8" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F8" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.71695464261996</v>
+        <v>3.529005129425744</v>
       </c>
       <c r="D9" t="n">
-        <v>17.74888862535997</v>
+        <v>2.884194401620995</v>
       </c>
       <c r="E9" t="n">
-        <v>12.48961226121472</v>
+        <v>2.029561992447392</v>
       </c>
       <c r="F9" t="n">
-        <v>11.18750891734828</v>
+        <v>1.817970199069095</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
